--- a/flaskbackend/2026년1월_결측다양_v5.xlsx
+++ b/flaskbackend/2026년1월_결측다양_v5.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KDT48\Desktop\python\DAY_9\project\PROJECT\IljiProject_v2\IljiProject_v2\flaskbackend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KDT48\Desktop\python\DAY_9\project\PROJECT\IljiProject_fin\IljiProject_v2\iljiproject\flaskbackend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A314450-6A96-443F-BC02-5F998C9E5640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C49A3B-AFDD-4ED8-8472-31FAB49310E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$918</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1226,6 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E918"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1250,7 +1254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1100003</v>
       </c>
@@ -1267,7 +1271,7 @@
         <v>-843873</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1100003</v>
       </c>
@@ -1284,7 +1288,7 @@
         <v>143428237</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1100003</v>
       </c>
@@ -1301,7 +1305,7 @@
         <v>15680020</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1100003</v>
       </c>
@@ -1332,10 +1336,10 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>736137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1100003</v>
       </c>
@@ -1352,7 +1356,7 @@
         <v>544680</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>1100003</v>
       </c>
@@ -1369,7 +1373,7 @@
         <v>21407</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1100003</v>
       </c>
@@ -1386,7 +1390,7 @@
         <v>757340</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1100003</v>
       </c>
@@ -1403,7 +1407,7 @@
         <v>9111210</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>1100003</v>
       </c>
@@ -1420,7 +1424,7 @@
         <v>366123</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>1100003</v>
       </c>
@@ -1437,7 +1441,7 @@
         <v>80527</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>1100003</v>
       </c>
@@ -1454,7 +1458,7 @@
         <v>446873</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>1100003</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>29866943</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>1100003</v>
       </c>
@@ -1488,7 +1492,7 @@
         <v>2488893</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>1100003</v>
       </c>
@@ -1505,7 +1509,7 @@
         <v>2544570</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1100003</v>
       </c>
@@ -1522,7 +1526,7 @@
         <v>107720</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1100003</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>8512917</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1100003</v>
       </c>
@@ -1556,7 +1560,7 @@
         <v>781143</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1100003</v>
       </c>
@@ -1573,7 +1577,7 @@
         <v>41850</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1100003</v>
       </c>
@@ -1590,7 +1594,7 @@
         <v>841133</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1100003</v>
       </c>
@@ -1607,7 +1611,7 @@
         <v>2621903</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1110001</v>
       </c>
@@ -1624,7 +1628,7 @@
         <v>5007</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1110001</v>
       </c>
@@ -1641,7 +1645,7 @@
         <v>76647</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1110002</v>
       </c>
@@ -1658,7 +1662,7 @@
         <v>4186130</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1110002</v>
       </c>
@@ -1675,7 +1679,7 @@
         <v>348840</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1110002</v>
       </c>
@@ -1692,7 +1696,7 @@
         <v>276513</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1110002</v>
       </c>
@@ -1709,7 +1713,7 @@
         <v>20923</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1110003</v>
       </c>
@@ -1726,7 +1730,7 @@
         <v>3249800</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1110003</v>
       </c>
@@ -1743,7 +1747,7 @@
         <v>16250</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1110004</v>
       </c>
@@ -1760,7 +1764,7 @@
         <v>16617397</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1110004</v>
       </c>
@@ -1777,7 +1781,7 @@
         <v>2724240</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1110004</v>
       </c>
@@ -1794,7 +1798,7 @@
         <v>1127503</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1110004</v>
       </c>
@@ -1811,7 +1815,7 @@
         <v>86787</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1110005</v>
       </c>
@@ -1828,7 +1832,7 @@
         <v>-104218233</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1110005</v>
       </c>
@@ -1845,7 +1849,7 @@
         <v>-85917470</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1110005</v>
       </c>
@@ -1862,7 +1866,7 @@
         <v>-86652150</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1110005</v>
       </c>
@@ -1879,7 +1883,7 @@
         <v>-147094753</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1110005</v>
       </c>
@@ -1896,7 +1900,7 @@
         <v>-153803</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1110005</v>
       </c>
@@ -1913,7 +1917,7 @@
         <v>-74342883</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1110005</v>
       </c>
@@ -1930,7 +1934,7 @@
         <v>-79859083</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1110005</v>
       </c>
@@ -1947,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1110005</v>
       </c>
@@ -1964,7 +1968,7 @@
         <v>-35797757</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1110005</v>
       </c>
@@ -1981,7 +1985,7 @@
         <v>1053953</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1110005</v>
       </c>
@@ -1998,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1110005</v>
       </c>
@@ -2015,7 +2019,7 @@
         <v>15706600</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1110005</v>
       </c>
@@ -2032,7 +2036,7 @@
         <v>2307223</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1110005</v>
       </c>
@@ -2049,7 +2053,7 @@
         <v>1931523</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1110005</v>
       </c>
@@ -2080,10 +2084,10 @@
         <v>100</v>
       </c>
       <c r="E50">
-        <v>736137</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1110005</v>
       </c>
@@ -2100,7 +2104,7 @@
         <v>17707</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1110005</v>
       </c>
@@ -2117,7 +2121,7 @@
         <v>474200</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1110005</v>
       </c>
@@ -2134,7 +2138,7 @@
         <v>92677</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1110005</v>
       </c>
@@ -2151,7 +2155,7 @@
         <v>105750</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1110005</v>
       </c>
@@ -2168,7 +2172,7 @@
         <v>14981440</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1110005</v>
       </c>
@@ -2185,7 +2189,7 @@
         <v>1071958973</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1110005</v>
       </c>
@@ -2202,7 +2206,7 @@
         <v>18697</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1110005</v>
       </c>
@@ -2219,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1110005</v>
       </c>
@@ -2236,7 +2240,7 @@
         <v>-632330</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1110005</v>
       </c>
@@ -2253,7 +2257,7 @@
         <v>-15604310</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1110005</v>
       </c>
@@ -2270,7 +2274,7 @@
         <v>-181917</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1110005</v>
       </c>
@@ -2287,7 +2291,7 @@
         <v>181223</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1110005</v>
       </c>
@@ -2304,7 +2308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1110005</v>
       </c>
@@ -2321,7 +2325,7 @@
         <v>383612533</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1110005</v>
       </c>
@@ -2338,7 +2342,7 @@
         <v>160481670</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1110005</v>
       </c>
@@ -2355,7 +2359,7 @@
         <v>969790</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1110005</v>
       </c>
@@ -2372,7 +2376,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1110005</v>
       </c>
@@ -2389,7 +2393,7 @@
         <v>3770817</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1110005</v>
       </c>
@@ -2406,7 +2410,7 @@
         <v>67544533</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1110005</v>
       </c>
@@ -2423,7 +2427,7 @@
         <v>380023</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1110005</v>
       </c>
@@ -2440,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1110005</v>
       </c>
@@ -2457,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1110005</v>
       </c>
@@ -2474,7 +2478,7 @@
         <v>2333587</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1110005</v>
       </c>
@@ -2491,7 +2495,7 @@
         <v>-465490647</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1110005</v>
       </c>
@@ -2508,7 +2512,7 @@
         <v>-230</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1110005</v>
       </c>
@@ -2525,7 +2529,7 @@
         <v>229917</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1110005</v>
       </c>
@@ -2542,7 +2546,7 @@
         <v>-67533</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1110005</v>
       </c>
@@ -2559,7 +2563,7 @@
         <v>-166800</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1110006</v>
       </c>
@@ -2576,7 +2580,7 @@
         <v>-3156473</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1110006</v>
       </c>
@@ -2593,7 +2597,7 @@
         <v>17029213</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1110006</v>
       </c>
@@ -2610,7 +2614,7 @@
         <v>2234940</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1110006</v>
       </c>
@@ -2627,7 +2631,7 @@
         <v>1984497</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1110006</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1110006</v>
       </c>
@@ -2675,10 +2679,10 @@
         <v>100</v>
       </c>
       <c r="E85">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1110006</v>
       </c>
@@ -2695,7 +2699,7 @@
         <v>178083</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1110006</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>-29243</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1110006</v>
       </c>
@@ -2729,7 +2733,7 @@
         <v>91040</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1110006</v>
       </c>
@@ -2746,7 +2750,7 @@
         <v>13184103</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1110006</v>
       </c>
@@ -2763,7 +2767,7 @@
         <v>15175823</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1110006</v>
       </c>
@@ -2780,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1110006</v>
       </c>
@@ -2797,7 +2801,7 @@
         <v>8710723</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1110006</v>
       </c>
@@ -2814,7 +2818,7 @@
         <v>159983</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1110006</v>
       </c>
@@ -2831,7 +2835,7 @@
         <v>59567</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1110006</v>
       </c>
@@ -2848,7 +2852,7 @@
         <v>97807</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1110006</v>
       </c>
@@ -2865,7 +2869,7 @@
         <v>271530</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1110006</v>
       </c>
@@ -2882,7 +2886,7 @@
         <v>681513</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1110006</v>
       </c>
@@ -2899,7 +2903,7 @@
         <v>1841813</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1110006</v>
       </c>
@@ -2916,7 +2920,7 @@
         <v>681513</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1110007</v>
       </c>
@@ -2933,7 +2937,7 @@
         <v>-123733</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1110007</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>36701807</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>1110007</v>
       </c>
@@ -2967,7 +2971,7 @@
         <v>4263707</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>1110007</v>
       </c>
@@ -2984,7 +2988,7 @@
         <v>4169487</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>1110007</v>
       </c>
@@ -3001,7 +3005,7 @@
         <v>3552970</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>1110007</v>
       </c>
@@ -3018,7 +3022,7 @@
         <v>6543720</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>1110007</v>
       </c>
@@ -3035,7 +3039,7 @@
         <v>318657</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>1110007</v>
       </c>
@@ -3052,7 +3056,7 @@
         <v>1882620</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>1110007</v>
       </c>
@@ -3069,7 +3073,7 @@
         <v>1121467</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>1110007</v>
       </c>
@@ -3086,7 +3090,7 @@
         <v>14387453</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>1110007</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>181713</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>1110007</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>1777990</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>1110007</v>
       </c>
@@ -3137,7 +3141,7 @@
         <v>1421403</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>1110007</v>
       </c>
@@ -3154,7 +3158,7 @@
         <v>12703</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>1110007</v>
       </c>
@@ -3171,7 +3175,7 @@
         <v>413353</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>1110007</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>1785133</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>1110007</v>
       </c>
@@ -3205,7 +3209,7 @@
         <v>389823</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>1110007</v>
       </c>
@@ -3222,7 +3226,7 @@
         <v>3583</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>1110007</v>
       </c>
@@ -3239,7 +3243,7 @@
         <v>131100</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>1110007</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>65103</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>1110007</v>
       </c>
@@ -3273,7 +3277,7 @@
         <v>640160</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>1110007</v>
       </c>
@@ -3290,7 +3294,7 @@
         <v>341687</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>1110007</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>90603</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>1110007</v>
       </c>
@@ -3324,7 +3328,7 @@
         <v>101867673</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>1110007</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>358690</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>1110007</v>
       </c>
@@ -3358,7 +3362,7 @@
         <v>236440</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>1110007</v>
       </c>
@@ -3375,7 +3379,7 @@
         <v>1068873</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>1110007</v>
       </c>
@@ -3392,7 +3396,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>1110007</v>
       </c>
@@ -3409,7 +3413,7 @@
         <v>228200</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>1110007</v>
       </c>
@@ -3426,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>1110007</v>
       </c>
@@ -3443,7 +3447,7 @@
         <v>59657</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>1110007</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>2880727</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>1110007</v>
       </c>
@@ -3477,7 +3481,7 @@
         <v>1606830</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>1110007</v>
       </c>
@@ -3494,7 +3498,7 @@
         <v>11177</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>1110007</v>
       </c>
@@ -3511,7 +3515,7 @@
         <v>20168480</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>1110007</v>
       </c>
@@ -3528,7 +3532,7 @@
         <v>27203760</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>1110007</v>
       </c>
@@ -3545,7 +3549,7 @@
         <v>20657243</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>1110007</v>
       </c>
@@ -3562,7 +3566,7 @@
         <v>815070</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>1110007</v>
       </c>
@@ -3579,7 +3583,7 @@
         <v>13912670</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>1110007</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>14265587</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>1110007</v>
       </c>
@@ -3613,7 +3617,7 @@
         <v>4362793</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>1110007</v>
       </c>
@@ -3630,7 +3634,7 @@
         <v>3384243</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>1110007</v>
       </c>
@@ -3647,7 +3651,7 @@
         <v>-4207</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>1110007</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>4724437</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>1110007</v>
       </c>
@@ -3681,7 +3685,7 @@
         <v>97960</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>1110007</v>
       </c>
@@ -3698,7 +3702,7 @@
         <v>637870</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>1110007</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>42090</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>1110007</v>
       </c>
@@ -3732,7 +3736,7 @@
         <v>1046483</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>1110007</v>
       </c>
@@ -3749,7 +3753,7 @@
         <v>9828110</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>1110007</v>
       </c>
@@ -3766,7 +3770,7 @@
         <v>32303</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>1110007</v>
       </c>
@@ -3783,7 +3787,7 @@
         <v>49293</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>1110007</v>
       </c>
@@ -3800,7 +3804,7 @@
         <v>4529140</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>1110007</v>
       </c>
@@ -3817,7 +3821,7 @@
         <v>136673</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>1110020</v>
       </c>
@@ -3834,7 +3838,7 @@
         <v>26500</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>1110020</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>1224203</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>1110020</v>
       </c>
@@ -3868,7 +3872,7 @@
         <v>32307</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>1110021</v>
       </c>
@@ -3885,7 +3889,7 @@
         <v>188200</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>1110021</v>
       </c>
@@ -3902,7 +3906,7 @@
         <v>5353</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>1110021</v>
       </c>
@@ -3933,10 +3937,10 @@
         <v>189</v>
       </c>
       <c r="E159">
-        <v>1104207</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>1110021</v>
       </c>
@@ -3953,7 +3957,7 @@
         <v>17670</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>1110021</v>
       </c>
@@ -3970,7 +3974,7 @@
         <v>34779903</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>1110021</v>
       </c>
@@ -3987,7 +3991,7 @@
         <v>2326410</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>1110021</v>
       </c>
@@ -4004,7 +4008,7 @@
         <v>32690</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>1110021</v>
       </c>
@@ -4021,7 +4025,7 @@
         <v>285317</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>1110021</v>
       </c>
@@ -4038,7 +4042,7 @@
         <v>599417</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>1110021</v>
       </c>
@@ -4055,7 +4059,7 @@
         <v>23755917</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>1110021</v>
       </c>
@@ -4072,7 +4076,7 @@
         <v>2749743</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>1110021</v>
       </c>
@@ -4089,7 +4093,7 @@
         <v>121863</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>1110021</v>
       </c>
@@ -4106,7 +4110,7 @@
         <v>2628317</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>1110021</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>69860</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>1110022</v>
       </c>
@@ -4140,7 +4144,7 @@
         <v>707613</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>1110022</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>10677</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>1110022</v>
       </c>
@@ -4188,10 +4192,10 @@
         <v>189</v>
       </c>
       <c r="E174">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>1110022</v>
       </c>
@@ -4208,7 +4212,7 @@
         <v>16767</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>1110022</v>
       </c>
@@ -4225,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>1110022</v>
       </c>
@@ -4242,7 +4246,7 @@
         <v>493353</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>1110022</v>
       </c>
@@ -4259,7 +4263,7 @@
         <v>22638093</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>1110022</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>2530417</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>1110022</v>
       </c>
@@ -4293,7 +4297,7 @@
         <v>110857</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>1110022</v>
       </c>
@@ -4310,7 +4314,7 @@
         <v>2562877</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>1110022</v>
       </c>
@@ -4327,7 +4331,7 @@
         <v>36810</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>1110023</v>
       </c>
@@ -4344,7 +4348,7 @@
         <v>26343</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>1110023</v>
       </c>
@@ -4361,7 +4365,7 @@
         <v>2225933</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>1110023</v>
       </c>
@@ -4378,7 +4382,7 @@
         <v>244737</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>1110023</v>
       </c>
@@ -4395,7 +4399,7 @@
         <v>11127</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>1110023</v>
       </c>
@@ -4412,7 +4416,7 @@
         <v>240750</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>1110024</v>
       </c>
@@ -4429,7 +4433,7 @@
         <v>-297890</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>1110024</v>
       </c>
@@ -4446,7 +4450,7 @@
         <v>106733</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>1110024</v>
       </c>
@@ -4477,10 +4481,10 @@
         <v>189</v>
       </c>
       <c r="E191">
-        <v>662527</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>1110024</v>
       </c>
@@ -4497,7 +4501,7 @@
         <v>4640273</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>1110024</v>
       </c>
@@ -4514,7 +4518,7 @@
         <v>174410</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>1110024</v>
       </c>
@@ -4531,7 +4535,7 @@
         <v>18893123</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>1110024</v>
       </c>
@@ -4548,7 +4552,7 @@
         <v>2268343</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>1110024</v>
       </c>
@@ -4565,7 +4569,7 @@
         <v>96347</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>1110024</v>
       </c>
@@ -4582,7 +4586,7 @@
         <v>2289687</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>1110024</v>
       </c>
@@ -4599,7 +4603,7 @@
         <v>76910</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>1110026</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>71930</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>1110026</v>
       </c>
@@ -4647,10 +4651,10 @@
         <v>189</v>
       </c>
       <c r="E201">
-        <v>1288243</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>1110026</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>27359573</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>1110026</v>
       </c>
@@ -4684,7 +4688,7 @@
         <v>496707</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>1110026</v>
       </c>
@@ -4701,7 +4705,7 @@
         <v>42315980</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>1110026</v>
       </c>
@@ -4718,7 +4722,7 @@
         <v>4329147</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>1110026</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>213563</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>1110026</v>
       </c>
@@ -4752,7 +4756,7 @@
         <v>4833620</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>1110026</v>
       </c>
@@ -4769,7 +4773,7 @@
         <v>27947</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>1110026</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>73613</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>1110030</v>
       </c>
@@ -4803,7 +4807,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>1110031</v>
       </c>
@@ -4820,7 +4824,7 @@
         <v>126757</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>1110031</v>
       </c>
@@ -4837,7 +4841,7 @@
         <v>3346027</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>1110031</v>
       </c>
@@ -4854,7 +4858,7 @@
         <v>18872880</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>1110031</v>
       </c>
@@ -4871,7 +4875,7 @@
         <v>1954807</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>1110031</v>
       </c>
@@ -4888,7 +4892,7 @@
         <v>121591860</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>1110031</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>17410</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>1110031</v>
       </c>
@@ -4936,10 +4940,10 @@
         <v>189</v>
       </c>
       <c r="E218">
-        <v>920173</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>1110031</v>
       </c>
@@ -4956,7 +4960,7 @@
         <v>2089667</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>1110031</v>
       </c>
@@ -4973,7 +4977,7 @@
         <v>549257</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>1110031</v>
       </c>
@@ -4990,7 +4994,7 @@
         <v>202057</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>1110031</v>
       </c>
@@ -5007,7 +5011,7 @@
         <v>14530280</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>1110031</v>
       </c>
@@ -5024,7 +5028,7 @@
         <v>3097240</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>1110031</v>
       </c>
@@ -5041,7 +5045,7 @@
         <v>100187</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>1110031</v>
       </c>
@@ -5058,7 +5062,7 @@
         <v>309807</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>1110031</v>
       </c>
@@ -5075,7 +5079,7 @@
         <v>936967</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>1110031</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>2404987</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>1110031</v>
       </c>
@@ -5109,7 +5113,7 @@
         <v>660680</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>1110031</v>
       </c>
@@ -5126,7 +5130,7 @@
         <v>7118673</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>1110031</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>997413</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>1110031</v>
       </c>
@@ -5160,7 +5164,7 @@
         <v>85510</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>1110031</v>
       </c>
@@ -5177,7 +5181,7 @@
         <v>5168850</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>1110031</v>
       </c>
@@ -5194,7 +5198,7 @@
         <v>2412090</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>1110031</v>
       </c>
@@ -5211,7 +5215,7 @@
         <v>18863</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>1110031</v>
       </c>
@@ -5228,7 +5232,7 @@
         <v>35530</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>1110031</v>
       </c>
@@ -5245,7 +5249,7 @@
         <v>442713</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>1110031</v>
       </c>
@@ -5262,7 +5266,7 @@
         <v>99187</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>1110031</v>
       </c>
@@ -5279,7 +5283,7 @@
         <v>97907</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>1110031</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>1355680</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>1110031</v>
       </c>
@@ -5313,7 +5317,7 @@
         <v>3326297</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>1110031</v>
       </c>
@@ -5330,7 +5334,7 @@
         <v>7650107</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>1110031</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>4835977</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>1110031</v>
       </c>
@@ -5364,7 +5368,7 @@
         <v>14703</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>1110032</v>
       </c>
@@ -5381,7 +5385,7 @@
         <v>-1330</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>1110032</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>81197</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>1110032</v>
       </c>
@@ -5415,7 +5419,7 @@
         <v>92500</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>1110032</v>
       </c>
@@ -5432,7 +5436,7 @@
         <v>157193</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>1110032</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>24245067</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>1110032</v>
       </c>
@@ -5466,7 +5470,7 @@
         <v>1959403</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>1110032</v>
       </c>
@@ -5483,7 +5487,7 @@
         <v>41687</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>1110032</v>
       </c>
@@ -5514,10 +5518,10 @@
         <v>189</v>
       </c>
       <c r="E252">
-        <v>478490</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>1110032</v>
       </c>
@@ -5534,7 +5538,7 @@
         <v>2622350</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>1110032</v>
       </c>
@@ -5551,7 +5555,7 @@
         <v>534227</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>1110032</v>
       </c>
@@ -5568,7 +5572,7 @@
         <v>29773</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>1110032</v>
       </c>
@@ -5585,7 +5589,7 @@
         <v>755733</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>1110032</v>
       </c>
@@ -5602,7 +5606,7 @@
         <v>114700</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>1110032</v>
       </c>
@@ -5619,7 +5623,7 @@
         <v>236437</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>1110032</v>
       </c>
@@ -5636,7 +5640,7 @@
         <v>115787</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>1110032</v>
       </c>
@@ -5653,7 +5657,7 @@
         <v>45410</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>1110032</v>
       </c>
@@ -5670,7 +5674,7 @@
         <v>8607</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>1110032</v>
       </c>
@@ -5687,7 +5691,7 @@
         <v>22307</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>1110032</v>
       </c>
@@ -5704,7 +5708,7 @@
         <v>274733</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>1110032</v>
       </c>
@@ -5721,7 +5725,7 @@
         <v>468760</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>1110032</v>
       </c>
@@ -5738,7 +5742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>1110032</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>49520</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>1110032</v>
       </c>
@@ -5772,7 +5776,7 @@
         <v>632953</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>1110032</v>
       </c>
@@ -5789,7 +5793,7 @@
         <v>106807</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>1110032</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>23720</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>1110032</v>
       </c>
@@ -5823,7 +5827,7 @@
         <v>90633</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>1110032</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>1370190</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>1110032</v>
       </c>
@@ -5857,7 +5861,7 @@
         <v>2094753</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>1110032</v>
       </c>
@@ -5874,7 +5878,7 @@
         <v>11777</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>1110032</v>
       </c>
@@ -5891,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>1110032</v>
       </c>
@@ -5908,7 +5912,7 @@
         <v>24453</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>1110032</v>
       </c>
@@ -5925,7 +5929,7 @@
         <v>22453</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>1110032</v>
       </c>
@@ -5942,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>1110034</v>
       </c>
@@ -5959,7 +5963,7 @@
         <v>-6981653</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>1110034</v>
       </c>
@@ -5976,7 +5980,7 @@
         <v>-5345107</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>1110034</v>
       </c>
@@ -5993,7 +5997,7 @@
         <v>30053</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>1110034</v>
       </c>
@@ -6010,7 +6014,7 @@
         <v>1789070</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>1110034</v>
       </c>
@@ -6027,7 +6031,7 @@
         <v>17706340</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>1110034</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>1389940</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>1110034</v>
       </c>
@@ -6061,7 +6065,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>1110034</v>
       </c>
@@ -6092,10 +6096,10 @@
         <v>189</v>
       </c>
       <c r="E286">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>1110034</v>
       </c>
@@ -6112,7 +6116,7 @@
         <v>1863290</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>1110034</v>
       </c>
@@ -6129,7 +6133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>1110034</v>
       </c>
@@ -6146,7 +6150,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>1110034</v>
       </c>
@@ -6163,7 +6167,7 @@
         <v>87633</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>1110034</v>
       </c>
@@ -6180,7 +6184,7 @@
         <v>1539767</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>1110034</v>
       </c>
@@ -6197,7 +6201,7 @@
         <v>7471750</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>1110034</v>
       </c>
@@ -6214,7 +6218,7 @@
         <v>62107</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>1110035</v>
       </c>
@@ -6231,7 +6235,7 @@
         <v>160650</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>1110035</v>
       </c>
@@ -6248,7 +6252,7 @@
         <v>59621317</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>1110035</v>
       </c>
@@ -6262,10 +6266,10 @@
         <v>219</v>
       </c>
       <c r="E296">
-        <v>17065040</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>1110035</v>
       </c>
@@ -6282,7 +6286,7 @@
         <v>4235257</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>1110035</v>
       </c>
@@ -6313,10 +6317,10 @@
         <v>189</v>
       </c>
       <c r="E299">
-        <v>1766733</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>1110035</v>
       </c>
@@ -6333,7 +6337,7 @@
         <v>5554187</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>1110035</v>
       </c>
@@ -6350,7 +6354,7 @@
         <v>257947</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>1110036</v>
       </c>
@@ -6367,7 +6371,7 @@
         <v>15027</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>1110036</v>
       </c>
@@ -6384,7 +6388,7 @@
         <v>51012703</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>1110036</v>
       </c>
@@ -6398,10 +6402,10 @@
         <v>219</v>
       </c>
       <c r="E304">
-        <v>12768657</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>1110036</v>
       </c>
@@ -6418,7 +6422,7 @@
         <v>3257887</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>1110036</v>
       </c>
@@ -6449,10 +6453,10 @@
         <v>189</v>
       </c>
       <c r="E307">
-        <v>1509083</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>1110036</v>
       </c>
@@ -6469,7 +6473,7 @@
         <v>4687807</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>1110036</v>
       </c>
@@ -6486,7 +6490,7 @@
         <v>3091067</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>1110036</v>
       </c>
@@ -6503,7 +6507,7 @@
         <v>215833</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>1110037</v>
       </c>
@@ -6520,7 +6524,7 @@
         <v>64573</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>1110037</v>
       </c>
@@ -6537,7 +6541,7 @@
         <v>119933533</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>1110037</v>
       </c>
@@ -6551,10 +6555,10 @@
         <v>219</v>
       </c>
       <c r="E313">
-        <v>31984477</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>1110037</v>
       </c>
@@ -6585,10 +6589,10 @@
         <v>189</v>
       </c>
       <c r="E315">
-        <v>2318840</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>1110037</v>
       </c>
@@ -6605,7 +6609,7 @@
         <v>10910390</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>1110037</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>534913</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>1110037</v>
       </c>
@@ -6639,7 +6643,7 @@
         <v>68001607</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>1110037</v>
       </c>
@@ -6656,7 +6660,7 @@
         <v>506797</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>1110038</v>
       </c>
@@ -6673,7 +6677,7 @@
         <v>16517</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>1110038</v>
       </c>
@@ -6690,7 +6694,7 @@
         <v>45535520</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>1110038</v>
       </c>
@@ -6704,10 +6708,10 @@
         <v>219</v>
       </c>
       <c r="E322">
-        <v>12113053</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>1110038</v>
       </c>
@@ -6724,7 +6728,7 @@
         <v>3583677</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>1110038</v>
       </c>
@@ -6755,10 +6759,10 @@
         <v>189</v>
       </c>
       <c r="E325">
-        <v>2245223</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>1110038</v>
       </c>
@@ -6775,7 +6779,7 @@
         <v>3948227</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>1110038</v>
       </c>
@@ -6792,7 +6796,7 @@
         <v>208417</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>1110039</v>
       </c>
@@ -6809,7 +6813,7 @@
         <v>49533</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>1110039</v>
       </c>
@@ -6826,7 +6830,7 @@
         <v>20389620</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>1110039</v>
       </c>
@@ -6840,10 +6844,10 @@
         <v>219</v>
       </c>
       <c r="E330">
-        <v>4729133</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>1110039</v>
       </c>
@@ -6874,10 +6878,10 @@
         <v>189</v>
       </c>
       <c r="E332">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>1110039</v>
       </c>
@@ -6894,7 +6898,7 @@
         <v>1798013</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>1110039</v>
       </c>
@@ -6911,7 +6915,7 @@
         <v>114090</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>1110039</v>
       </c>
@@ -6928,7 +6932,7 @@
         <v>626887</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>1110039</v>
       </c>
@@ -6945,7 +6949,7 @@
         <v>86313</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>1110040</v>
       </c>
@@ -6962,7 +6966,7 @@
         <v>58917</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>1110040</v>
       </c>
@@ -6979,7 +6983,7 @@
         <v>10332487</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>1110040</v>
       </c>
@@ -6993,10 +6997,10 @@
         <v>219</v>
       </c>
       <c r="E339">
-        <v>3783307</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>1110040</v>
       </c>
@@ -7013,7 +7017,7 @@
         <v>977363</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>1110040</v>
       </c>
@@ -7044,10 +7048,10 @@
         <v>189</v>
       </c>
       <c r="E342">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>1110040</v>
       </c>
@@ -7064,7 +7068,7 @@
         <v>1174310</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>1110040</v>
       </c>
@@ -7081,7 +7085,7 @@
         <v>53240</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>1110041</v>
       </c>
@@ -7098,7 +7102,7 @@
         <v>10366283</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>1110041</v>
       </c>
@@ -7112,10 +7116,10 @@
         <v>219</v>
       </c>
       <c r="E346">
-        <v>1891653</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>1110041</v>
       </c>
@@ -7132,7 +7136,7 @@
         <v>651573</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>1110041</v>
       </c>
@@ -7149,7 +7153,7 @@
         <v>42690</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>1110041</v>
       </c>
@@ -7166,7 +7170,7 @@
         <v>937773</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>1110041</v>
       </c>
@@ -7183,7 +7187,7 @@
         <v>41263</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>1110042</v>
       </c>
@@ -7200,7 +7204,7 @@
         <v>193280</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>1110042</v>
       </c>
@@ -7217,7 +7221,7 @@
         <v>241461783</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>1110042</v>
       </c>
@@ -7231,10 +7235,10 @@
         <v>219</v>
       </c>
       <c r="E353">
-        <v>62109693</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>1110042</v>
       </c>
@@ -7265,10 +7269,10 @@
         <v>189</v>
       </c>
       <c r="E355">
-        <v>3128590</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>1110042</v>
       </c>
@@ -7285,7 +7289,7 @@
         <v>21590323</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>1110042</v>
       </c>
@@ -7302,7 +7306,7 @@
         <v>40137</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>1110042</v>
       </c>
@@ -7319,7 +7323,7 @@
         <v>160680073</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>1110042</v>
       </c>
@@ -7336,7 +7340,7 @@
         <v>353710</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>1110042</v>
       </c>
@@ -7353,7 +7357,7 @@
         <v>-11672590</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>1110042</v>
       </c>
@@ -7370,7 +7374,7 @@
         <v>990573</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>1110043</v>
       </c>
@@ -7387,7 +7391,7 @@
         <v>-2149153</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>1110043</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>33023</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>1110043</v>
       </c>
@@ -7421,7 +7425,7 @@
         <v>2013560</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>1110043</v>
       </c>
@@ -7438,7 +7442,7 @@
         <v>249693</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>1110043</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>22343037</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>1110043</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>1948073</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>1110043</v>
       </c>
@@ -7489,7 +7493,7 @@
         <v>6190</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>1110043</v>
       </c>
@@ -7506,7 +7510,7 @@
         <v>149423</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>1110043</v>
       </c>
@@ -7523,7 +7527,7 @@
         <v>2492583</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>1110043</v>
       </c>
@@ -7540,7 +7544,7 @@
         <v>4787</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>1110043</v>
       </c>
@@ -7557,7 +7561,7 @@
         <v>235220</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>1110043</v>
       </c>
@@ -7574,7 +7578,7 @@
         <v>746517</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>1110043</v>
       </c>
@@ -7591,7 +7595,7 @@
         <v>109917</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>1110043</v>
       </c>
@@ -7608,7 +7612,7 @@
         <v>603637</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>1110043</v>
       </c>
@@ -7625,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>1110043</v>
       </c>
@@ -7642,7 +7646,7 @@
         <v>67372677</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>1110043</v>
       </c>
@@ -7659,7 +7663,7 @@
         <v>961293</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>1110043</v>
       </c>
@@ -7676,7 +7680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>1110043</v>
       </c>
@@ -7693,7 +7697,7 @@
         <v>45257</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>1110043</v>
       </c>
@@ -7710,7 +7714,7 @@
         <v>11877</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>1110044</v>
       </c>
@@ -7727,7 +7731,7 @@
         <v>14879113</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>1110044</v>
       </c>
@@ -7744,7 +7748,7 @@
         <v>1957297</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>1110044</v>
       </c>
@@ -7761,7 +7765,7 @@
         <v>1579587</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>1110044</v>
       </c>
@@ -7792,10 +7796,10 @@
         <v>100</v>
       </c>
       <c r="E386">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>1110044</v>
       </c>
@@ -7812,7 +7816,7 @@
         <v>74020</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>1110044</v>
       </c>
@@ -7829,7 +7833,7 @@
         <v>48037</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>1110044</v>
       </c>
@@ -7846,7 +7850,7 @@
         <v>15493</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>1110044</v>
       </c>
@@ -7863,7 +7867,7 @@
         <v>595280</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>1110044</v>
       </c>
@@ -7880,7 +7884,7 @@
         <v>706697</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>1110044</v>
       </c>
@@ -7897,7 +7901,7 @@
         <v>32560</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>1110044</v>
       </c>
@@ -7914,7 +7918,7 @@
         <v>1507977</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>1110044</v>
       </c>
@@ -7931,7 +7935,7 @@
         <v>1990787</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>1110044</v>
       </c>
@@ -7948,7 +7952,7 @@
         <v>1727740</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>1110044</v>
       </c>
@@ -7965,7 +7969,7 @@
         <v>480330</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>1110044</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>187083</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>1110044</v>
       </c>
@@ -7999,7 +8003,7 @@
         <v>15920</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>1110045</v>
       </c>
@@ -8016,7 +8020,7 @@
         <v>54136717</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400">
         <v>1110045</v>
       </c>
@@ -8030,10 +8034,10 @@
         <v>219</v>
       </c>
       <c r="E400">
-        <v>13714483</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401">
         <v>1110045</v>
       </c>
@@ -8050,7 +8054,7 @@
         <v>7167363</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402">
         <v>1110045</v>
       </c>
@@ -8081,10 +8085,10 @@
         <v>189</v>
       </c>
       <c r="E403">
-        <v>1582697</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404">
         <v>1110045</v>
       </c>
@@ -8101,7 +8105,7 @@
         <v>4966453</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405">
         <v>1110045</v>
       </c>
@@ -8118,7 +8122,7 @@
         <v>234557</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406">
         <v>1110046</v>
       </c>
@@ -8135,7 +8139,7 @@
         <v>32813757</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407">
         <v>1110046</v>
       </c>
@@ -8149,10 +8153,10 @@
         <v>219</v>
       </c>
       <c r="E407">
-        <v>13241570</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408">
         <v>1110046</v>
       </c>
@@ -8169,7 +8173,7 @@
         <v>1954727</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409">
         <v>1110046</v>
       </c>
@@ -8200,10 +8204,10 @@
         <v>189</v>
       </c>
       <c r="E410">
-        <v>920173</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411">
         <v>1110046</v>
       </c>
@@ -8220,7 +8224,7 @@
         <v>2859660</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412">
         <v>1110046</v>
       </c>
@@ -8237,7 +8241,7 @@
         <v>136310</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413">
         <v>1110047</v>
       </c>
@@ -8254,7 +8258,7 @@
         <v>116121143</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414">
         <v>1110047</v>
       </c>
@@ -8268,10 +8272,10 @@
         <v>219</v>
       </c>
       <c r="E414">
-        <v>34777907</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415">
         <v>1110047</v>
       </c>
@@ -8288,7 +8292,7 @@
         <v>18022530</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416">
         <v>1110047</v>
       </c>
@@ -8319,10 +8323,10 @@
         <v>189</v>
       </c>
       <c r="E417">
-        <v>3165397</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418">
         <v>1110047</v>
       </c>
@@ -8339,7 +8343,7 @@
         <v>10548150</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419">
         <v>1110047</v>
       </c>
@@ -8356,7 +8360,7 @@
         <v>472277</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420">
         <v>1110048</v>
       </c>
@@ -8373,7 +8377,7 @@
         <v>2990747</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421">
         <v>1110048</v>
       </c>
@@ -8390,7 +8394,7 @@
         <v>249223</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422">
         <v>1110048</v>
       </c>
@@ -8407,7 +8411,7 @@
         <v>344277</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423">
         <v>1110048</v>
       </c>
@@ -8424,7 +8428,7 @@
         <v>14950</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424">
         <v>1110049</v>
       </c>
@@ -8441,7 +8445,7 @@
         <v>34633</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425">
         <v>1110060</v>
       </c>
@@ -8458,7 +8462,7 @@
         <v>48713</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426">
         <v>1110060</v>
       </c>
@@ -8475,7 +8479,7 @@
         <v>95397</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427">
         <v>1110061</v>
       </c>
@@ -8492,7 +8496,7 @@
         <v>34293</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428">
         <v>1110061</v>
       </c>
@@ -8509,7 +8513,7 @@
         <v>303450</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429">
         <v>1110062</v>
       </c>
@@ -8526,7 +8530,7 @@
         <v>-5511687</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430">
         <v>1110062</v>
       </c>
@@ -8543,7 +8547,7 @@
         <v>8033</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431">
         <v>1110062</v>
       </c>
@@ -8560,7 +8564,7 @@
         <v>401777</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432">
         <v>1110062</v>
       </c>
@@ -8577,7 +8581,7 @@
         <v>1714737</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433">
         <v>1110062</v>
       </c>
@@ -8594,7 +8598,7 @@
         <v>45840747</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434">
         <v>1110062</v>
       </c>
@@ -8611,7 +8615,7 @@
         <v>3193753</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435">
         <v>1110062</v>
       </c>
@@ -8642,10 +8646,10 @@
         <v>189</v>
       </c>
       <c r="E436">
-        <v>920173</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437">
         <v>1110062</v>
       </c>
@@ -8662,7 +8666,7 @@
         <v>5026753</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438">
         <v>1110062</v>
       </c>
@@ -8679,7 +8683,7 @@
         <v>819747</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439">
         <v>1110062</v>
       </c>
@@ -8696,7 +8700,7 @@
         <v>47725623</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440">
         <v>1110062</v>
       </c>
@@ -8713,7 +8717,7 @@
         <v>-2670853</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441">
         <v>1110062</v>
       </c>
@@ -8730,7 +8734,7 @@
         <v>228993</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442">
         <v>1110062</v>
       </c>
@@ -8747,7 +8751,7 @@
         <v>209587</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443">
         <v>1110062</v>
       </c>
@@ -8764,7 +8768,7 @@
         <v>201360</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444">
         <v>1110062</v>
       </c>
@@ -8781,7 +8785,7 @@
         <v>78720</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445">
         <v>1110062</v>
       </c>
@@ -8798,7 +8802,7 @@
         <v>104987</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446">
         <v>1110062</v>
       </c>
@@ -8815,7 +8819,7 @@
         <v>130253</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447">
         <v>1110062</v>
       </c>
@@ -8832,7 +8836,7 @@
         <v>55890</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448">
         <v>1110062</v>
       </c>
@@ -8849,7 +8853,7 @@
         <v>32630</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449">
         <v>1110062</v>
       </c>
@@ -8866,7 +8870,7 @@
         <v>53800</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450">
         <v>1110062</v>
       </c>
@@ -8883,7 +8887,7 @@
         <v>182160</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451">
         <v>1110080</v>
       </c>
@@ -8900,7 +8904,7 @@
         <v>-2477677</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452">
         <v>1110080</v>
       </c>
@@ -8917,7 +8921,7 @@
         <v>-28527</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453">
         <v>1110080</v>
       </c>
@@ -8934,7 +8938,7 @@
         <v>-2873687</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454">
         <v>1110080</v>
       </c>
@@ -8951,7 +8955,7 @@
         <v>-151077</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455">
         <v>1110080</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>-19906327</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456">
         <v>1110080</v>
       </c>
@@ -8985,7 +8989,7 @@
         <v>-3518880</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457">
         <v>1110080</v>
       </c>
@@ -9002,7 +9006,7 @@
         <v>-798700</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458">
         <v>1110080</v>
       </c>
@@ -9019,7 +9023,7 @@
         <v>17470007</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459">
         <v>1110080</v>
       </c>
@@ -9036,7 +9040,7 @@
         <v>2771010</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460">
         <v>1110080</v>
       </c>
@@ -9053,7 +9057,7 @@
         <v>1918850</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461">
         <v>1110080</v>
       </c>
@@ -9070,7 +9074,7 @@
         <v>131263</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462">
         <v>1110080</v>
       </c>
@@ -9087,7 +9091,7 @@
         <v>38867</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463">
         <v>1110080</v>
       </c>
@@ -9104,7 +9108,7 @@
         <v>85910</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464">
         <v>1110080</v>
       </c>
@@ -9121,7 +9125,7 @@
         <v>61587</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465">
         <v>1110080</v>
       </c>
@@ -9138,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A466">
         <v>1110080</v>
       </c>
@@ -9155,7 +9159,7 @@
         <v>53960</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467">
         <v>1110080</v>
       </c>
@@ -9172,7 +9176,7 @@
         <v>7366383</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468">
         <v>1110080</v>
       </c>
@@ -9189,7 +9193,7 @@
         <v>27167</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469">
         <v>1110080</v>
       </c>
@@ -9206,7 +9210,7 @@
         <v>76967</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470">
         <v>1110080</v>
       </c>
@@ -9223,7 +9227,7 @@
         <v>119150</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471">
         <v>1110080</v>
       </c>
@@ -9240,7 +9244,7 @@
         <v>4205140</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472">
         <v>1110080</v>
       </c>
@@ -9257,7 +9261,7 @@
         <v>9037</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>1110090</v>
       </c>
@@ -9274,7 +9278,7 @@
         <v>47950</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474">
         <v>1110090</v>
       </c>
@@ -9291,7 +9295,7 @@
         <v>27710</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475">
         <v>1110091</v>
       </c>
@@ -9308,7 +9312,7 @@
         <v>24943803</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A476">
         <v>1110091</v>
       </c>
@@ -9325,7 +9329,7 @@
         <v>3011600</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A477">
         <v>1110091</v>
       </c>
@@ -9342,7 +9346,7 @@
         <v>2672653</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A478">
         <v>1110091</v>
       </c>
@@ -9373,10 +9377,10 @@
         <v>100</v>
       </c>
       <c r="E479">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480">
         <v>1110091</v>
       </c>
@@ -9393,7 +9397,7 @@
         <v>170820</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481">
         <v>1110091</v>
       </c>
@@ -9410,7 +9414,7 @@
         <v>968740</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482">
         <v>1110091</v>
       </c>
@@ -9427,7 +9431,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483">
         <v>1110091</v>
       </c>
@@ -9444,7 +9448,7 @@
         <v>122780</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484">
         <v>1110091</v>
       </c>
@@ -9461,7 +9465,7 @@
         <v>269090</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485">
         <v>1110091</v>
       </c>
@@ -9478,7 +9482,7 @@
         <v>477203</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486">
         <v>1110091</v>
       </c>
@@ -9495,7 +9499,7 @@
         <v>1687943</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487">
         <v>1110091</v>
       </c>
@@ -9512,7 +9516,7 @@
         <v>13983</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488">
         <v>1110091</v>
       </c>
@@ -9529,7 +9533,7 @@
         <v>8273263</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489">
         <v>1110092</v>
       </c>
@@ -9546,7 +9550,7 @@
         <v>-3388203</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490">
         <v>1110092</v>
       </c>
@@ -9563,7 +9567,7 @@
         <v>122583</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491">
         <v>1110092</v>
       </c>
@@ -9580,7 +9584,7 @@
         <v>33127</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492">
         <v>1110092</v>
       </c>
@@ -9597,7 +9601,7 @@
         <v>87480</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493">
         <v>1110092</v>
       </c>
@@ -9614,7 +9618,7 @@
         <v>53927</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A494">
         <v>1110092</v>
       </c>
@@ -9631,7 +9635,7 @@
         <v>41410</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495">
         <v>1110092</v>
       </c>
@@ -9648,7 +9652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A496">
         <v>1110092</v>
       </c>
@@ -9665,7 +9669,7 @@
         <v>86947</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497">
         <v>1110092</v>
       </c>
@@ -9682,7 +9686,7 @@
         <v>5153</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498">
         <v>1110092</v>
       </c>
@@ -9699,7 +9703,7 @@
         <v>18403</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499">
         <v>1110092</v>
       </c>
@@ -9716,7 +9720,7 @@
         <v>-3420750</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500">
         <v>1110092</v>
       </c>
@@ -9733,7 +9737,7 @@
         <v>56890</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501">
         <v>1110092</v>
       </c>
@@ -9750,7 +9754,7 @@
         <v>3808017</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502">
         <v>1110092</v>
       </c>
@@ -9767,7 +9771,7 @@
         <v>36000443</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503">
         <v>1110092</v>
       </c>
@@ -9784,7 +9788,7 @@
         <v>2866457</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504">
         <v>1110092</v>
       </c>
@@ -9815,10 +9819,10 @@
         <v>189</v>
       </c>
       <c r="E505">
-        <v>920173</v>
-      </c>
-    </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506">
         <v>1110092</v>
       </c>
@@ -9835,7 +9839,7 @@
         <v>4050370</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507">
         <v>1110092</v>
       </c>
@@ -9852,7 +9856,7 @@
         <v>517123</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508">
         <v>1110092</v>
       </c>
@@ -9869,7 +9873,7 @@
         <v>18845153</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509">
         <v>1110092</v>
       </c>
@@ -9886,7 +9890,7 @@
         <v>183810</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510">
         <v>1110092</v>
       </c>
@@ -9903,7 +9907,7 @@
         <v>105930</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511">
         <v>1110092</v>
       </c>
@@ -9920,7 +9924,7 @@
         <v>82047</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512">
         <v>1110092</v>
       </c>
@@ -9937,7 +9941,7 @@
         <v>17603</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513">
         <v>1110092</v>
       </c>
@@ -9954,7 +9958,7 @@
         <v>262310</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514">
         <v>1110092</v>
       </c>
@@ -9971,7 +9975,7 @@
         <v>68187</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515">
         <v>1110092</v>
       </c>
@@ -9988,7 +9992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516">
         <v>1110092</v>
       </c>
@@ -10005,7 +10009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517">
         <v>1110092</v>
       </c>
@@ -10022,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518">
         <v>1110092</v>
       </c>
@@ -10039,7 +10043,7 @@
         <v>77403</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519">
         <v>1110092</v>
       </c>
@@ -10056,7 +10060,7 @@
         <v>306087</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520">
         <v>1110092</v>
       </c>
@@ -10073,7 +10077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521">
         <v>1110092</v>
       </c>
@@ -10090,7 +10094,7 @@
         <v>357147</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522">
         <v>1110092</v>
       </c>
@@ -10107,7 +10111,7 @@
         <v>69860</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523">
         <v>1110093</v>
       </c>
@@ -10124,7 +10128,7 @@
         <v>12908443</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524">
         <v>1110093</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>1057913</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A525">
         <v>1110093</v>
       </c>
@@ -10158,7 +10162,7 @@
         <v>1402220</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A526">
         <v>1110093</v>
       </c>
@@ -10175,7 +10179,7 @@
         <v>64127</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527">
         <v>1110094</v>
       </c>
@@ -10192,7 +10196,7 @@
         <v>8667313</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A528">
         <v>1110094</v>
       </c>
@@ -10209,7 +10213,7 @@
         <v>1408227</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529">
         <v>1110094</v>
       </c>
@@ -10226,7 +10230,7 @@
         <v>907493</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530">
         <v>1110094</v>
       </c>
@@ -10243,7 +10247,7 @@
         <v>42340</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531">
         <v>1110100</v>
       </c>
@@ -10260,7 +10264,7 @@
         <v>1170833</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532">
         <v>1110100</v>
       </c>
@@ -10291,10 +10295,10 @@
         <v>100</v>
       </c>
       <c r="E533">
-        <v>552107</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534">
         <v>1110101</v>
       </c>
@@ -10311,7 +10315,7 @@
         <v>4652003</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A535">
         <v>1110101</v>
       </c>
@@ -10328,7 +10332,7 @@
         <v>6242463</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A536">
         <v>1110101</v>
       </c>
@@ -10345,7 +10349,7 @@
         <v>5181690</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A537">
         <v>1110101</v>
       </c>
@@ -10362,7 +10366,7 @@
         <v>66787</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A538">
         <v>1110101</v>
       </c>
@@ -10379,7 +10383,7 @@
         <v>21710</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A539">
         <v>1110101</v>
       </c>
@@ -10396,7 +10400,7 @@
         <v>150703</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A540">
         <v>1110102</v>
       </c>
@@ -10413,7 +10417,7 @@
         <v>4683343</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A541">
         <v>1110102</v>
       </c>
@@ -10430,7 +10434,7 @@
         <v>502137</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A542">
         <v>1110102</v>
       </c>
@@ -10461,10 +10465,10 @@
         <v>100</v>
       </c>
       <c r="E543">
-        <v>552107</v>
-      </c>
-    </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A544">
         <v>1110102</v>
       </c>
@@ -10481,7 +10485,7 @@
         <v>25497</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A545">
         <v>1110102</v>
       </c>
@@ -10498,7 +10502,7 @@
         <v>27717</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A546">
         <v>1110121</v>
       </c>
@@ -10515,7 +10519,7 @@
         <v>27601737</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A547">
         <v>1110121</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>2953477</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A548">
         <v>1110121</v>
       </c>
@@ -10549,7 +10553,7 @@
         <v>2924800</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A549">
         <v>1110121</v>
       </c>
@@ -10580,10 +10584,10 @@
         <v>100</v>
       </c>
       <c r="E550">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551">
         <v>1110121</v>
       </c>
@@ -10600,7 +10604,7 @@
         <v>176910</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A552">
         <v>1110121</v>
       </c>
@@ -10617,7 +10621,7 @@
         <v>132713</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553">
         <v>1110121</v>
       </c>
@@ -10634,7 +10638,7 @@
         <v>3177</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554">
         <v>1110121</v>
       </c>
@@ -10651,7 +10655,7 @@
         <v>115067</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A555">
         <v>1110121</v>
       </c>
@@ -10668,7 +10672,7 @@
         <v>240217</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A556">
         <v>1110122</v>
       </c>
@@ -10699,10 +10703,10 @@
         <v>189</v>
       </c>
       <c r="E557">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A558">
         <v>1110122</v>
       </c>
@@ -10719,7 +10723,7 @@
         <v>8380</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559">
         <v>1110122</v>
       </c>
@@ -10736,7 +10740,7 @@
         <v>3910</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A560">
         <v>1110122</v>
       </c>
@@ -10753,7 +10757,7 @@
         <v>53223</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A561">
         <v>1110122</v>
       </c>
@@ -10770,7 +10774,7 @@
         <v>78857</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A562">
         <v>1110122</v>
       </c>
@@ -10787,7 +10791,7 @@
         <v>155030</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A563">
         <v>1110122</v>
       </c>
@@ -10804,7 +10808,7 @@
         <v>17562190</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A564">
         <v>1110122</v>
       </c>
@@ -10821,7 +10825,7 @@
         <v>2015280</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565">
         <v>1110122</v>
       </c>
@@ -10838,7 +10842,7 @@
         <v>85900</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A566">
         <v>1110122</v>
       </c>
@@ -10855,7 +10859,7 @@
         <v>1980450</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A567">
         <v>1110123</v>
       </c>
@@ -10886,10 +10890,10 @@
         <v>189</v>
       </c>
       <c r="E568">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569">
         <v>1110123</v>
       </c>
@@ -10906,7 +10910,7 @@
         <v>927990</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A570">
         <v>1110123</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>65920</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A571">
         <v>1110123</v>
       </c>
@@ -10940,7 +10944,7 @@
         <v>22751863</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A572">
         <v>1110123</v>
       </c>
@@ -10957,7 +10961,7 @@
         <v>2285337</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A573">
         <v>1110123</v>
       </c>
@@ -10974,7 +10978,7 @@
         <v>115193</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574">
         <v>1110123</v>
       </c>
@@ -10991,7 +10995,7 @@
         <v>2593500</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575">
         <v>1110123</v>
       </c>
@@ -11008,7 +11012,7 @@
         <v>16417</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576">
         <v>1110124</v>
       </c>
@@ -11025,7 +11029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577">
         <v>1110124</v>
       </c>
@@ -11056,10 +11060,10 @@
         <v>189</v>
       </c>
       <c r="E578">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579">
         <v>1110124</v>
       </c>
@@ -11076,7 +11080,7 @@
         <v>22227</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A580">
         <v>1110124</v>
       </c>
@@ -11093,7 +11097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A581">
         <v>1110124</v>
       </c>
@@ -11110,7 +11114,7 @@
         <v>327820</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582">
         <v>1110124</v>
       </c>
@@ -11127,7 +11131,7 @@
         <v>24872577</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A583">
         <v>1110124</v>
       </c>
@@ -11144,7 +11148,7 @@
         <v>2431387</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A584">
         <v>1110124</v>
       </c>
@@ -11161,7 +11165,7 @@
         <v>123270</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A585">
         <v>1110124</v>
       </c>
@@ -11178,7 +11182,7 @@
         <v>2728173</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586">
         <v>1110125</v>
       </c>
@@ -11195,7 +11199,7 @@
         <v>64043</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587">
         <v>1110125</v>
       </c>
@@ -11212,7 +11216,7 @@
         <v>15248683</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588">
         <v>1110125</v>
       </c>
@@ -11229,7 +11233,7 @@
         <v>1037110</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589">
         <v>1110125</v>
       </c>
@@ -11246,7 +11250,7 @@
         <v>1607153</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590">
         <v>1110125</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>61007</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A591">
         <v>1120001</v>
       </c>
@@ -11280,7 +11284,7 @@
         <v>14907037</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A592">
         <v>1120002</v>
       </c>
@@ -11297,7 +11301,7 @@
         <v>7671450</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A593">
         <v>1120002</v>
       </c>
@@ -11314,7 +11318,7 @@
         <v>129130</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A594">
         <v>1200001</v>
       </c>
@@ -11331,7 +11335,7 @@
         <v>16428013</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A595">
         <v>1200001</v>
       </c>
@@ -11362,10 +11366,10 @@
         <v>189</v>
       </c>
       <c r="E596">
-        <v>1288243</v>
-      </c>
-    </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597">
         <v>1200001</v>
       </c>
@@ -11382,7 +11386,7 @@
         <v>1618290</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598">
         <v>1200001</v>
       </c>
@@ -11399,7 +11403,7 @@
         <v>86817</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599">
         <v>1210001</v>
       </c>
@@ -11416,7 +11420,7 @@
         <v>-419170</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600">
         <v>1210001</v>
       </c>
@@ -11433,7 +11437,7 @@
         <v>10857</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A601">
         <v>1210002</v>
       </c>
@@ -11450,7 +11454,7 @@
         <v>13382847</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A602">
         <v>1210002</v>
       </c>
@@ -11467,7 +11471,7 @@
         <v>1043493</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603">
         <v>1210002</v>
       </c>
@@ -11484,7 +11488,7 @@
         <v>13383</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604">
         <v>1210002</v>
       </c>
@@ -11515,10 +11519,10 @@
         <v>189</v>
       </c>
       <c r="E605">
-        <v>368070</v>
-      </c>
-    </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A606">
         <v>1210002</v>
       </c>
@@ -11535,7 +11539,7 @@
         <v>1476733</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607">
         <v>1210002</v>
       </c>
@@ -11552,7 +11556,7 @@
         <v>16033</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608">
         <v>1210002</v>
       </c>
@@ -11569,7 +11573,7 @@
         <v>4374487</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609">
         <v>1210002</v>
       </c>
@@ -11586,7 +11590,7 @@
         <v>65477</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A610">
         <v>1210002</v>
       </c>
@@ -11603,7 +11607,7 @@
         <v>110420</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611">
         <v>1210002</v>
       </c>
@@ -11620,7 +11624,7 @@
         <v>56947</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A612">
         <v>1210002</v>
       </c>
@@ -11637,7 +11641,7 @@
         <v>511463</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A613">
         <v>1210002</v>
       </c>
@@ -11654,7 +11658,7 @@
         <v>13720</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A614">
         <v>1210003</v>
       </c>
@@ -11671,7 +11675,7 @@
         <v>11291697</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A615">
         <v>1210003</v>
       </c>
@@ -11688,7 +11692,7 @@
         <v>946940</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616">
         <v>1210003</v>
       </c>
@@ -11705,7 +11709,7 @@
         <v>1261790</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A617">
         <v>1210003</v>
       </c>
@@ -11722,7 +11726,7 @@
         <v>31250</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618">
         <v>1210003</v>
       </c>
@@ -11753,10 +11757,10 @@
         <v>100</v>
       </c>
       <c r="E619">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A620">
         <v>1210003</v>
       </c>
@@ -11773,7 +11777,7 @@
         <v>167440</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A621">
         <v>1210003</v>
       </c>
@@ -11790,7 +11794,7 @@
         <v>12947907</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A622">
         <v>1210003</v>
       </c>
@@ -11807,7 +11811,7 @@
         <v>56447</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A623">
         <v>1210003</v>
       </c>
@@ -11824,7 +11828,7 @@
         <v>433853</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A624">
         <v>1210003</v>
       </c>
@@ -11841,7 +11845,7 @@
         <v>152527</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A625">
         <v>1210003</v>
       </c>
@@ -11858,7 +11862,7 @@
         <v>69860</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A626">
         <v>1210003</v>
       </c>
@@ -11875,7 +11879,7 @@
         <v>94017</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A627">
         <v>1210003</v>
       </c>
@@ -11892,7 +11896,7 @@
         <v>5520843</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A628">
         <v>1210003</v>
       </c>
@@ -11909,7 +11913,7 @@
         <v>3023467</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A629">
         <v>1210003</v>
       </c>
@@ -11926,7 +11930,7 @@
         <v>79720</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A630">
         <v>1210003</v>
       </c>
@@ -11943,7 +11947,7 @@
         <v>1666987</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A631">
         <v>1210003</v>
       </c>
@@ -11960,7 +11964,7 @@
         <v>39243687</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632">
         <v>1210003</v>
       </c>
@@ -11977,7 +11981,7 @@
         <v>7269910</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A633">
         <v>1210003</v>
       </c>
@@ -11994,7 +11998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A634">
         <v>1210003</v>
       </c>
@@ -12011,7 +12015,7 @@
         <v>1640090</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A635">
         <v>1210003</v>
       </c>
@@ -12028,7 +12032,7 @@
         <v>44396263</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A636">
         <v>1210003</v>
       </c>
@@ -12045,7 +12049,7 @@
         <v>18063253</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A637">
         <v>1210003</v>
       </c>
@@ -12062,7 +12066,7 @@
         <v>3726250</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A638">
         <v>1210003</v>
       </c>
@@ -12079,7 +12083,7 @@
         <v>1940053</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A639">
         <v>1210003</v>
       </c>
@@ -12096,7 +12100,7 @@
         <v>-27705953</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640">
         <v>1210003</v>
       </c>
@@ -12113,7 +12117,7 @@
         <v>8420103</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A641">
         <v>1210003</v>
       </c>
@@ -12130,7 +12134,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642">
         <v>1210003</v>
       </c>
@@ -12147,7 +12151,7 @@
         <v>115437</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A643">
         <v>1210003</v>
       </c>
@@ -12164,7 +12168,7 @@
         <v>301733</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A644">
         <v>1210003</v>
       </c>
@@ -12181,7 +12185,7 @@
         <v>144780</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A645">
         <v>1210003</v>
       </c>
@@ -12198,7 +12202,7 @@
         <v>184633</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A646">
         <v>1210003</v>
       </c>
@@ -12215,7 +12219,7 @@
         <v>18990883</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A647">
         <v>1210003</v>
       </c>
@@ -12232,7 +12236,7 @@
         <v>2978013</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A648">
         <v>1210003</v>
       </c>
@@ -12249,7 +12253,7 @@
         <v>1805747</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649">
         <v>1210003</v>
       </c>
@@ -12266,7 +12270,7 @@
         <v>13050</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A650">
         <v>1210003</v>
       </c>
@@ -12283,7 +12287,7 @@
         <v>932593</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651">
         <v>1210003</v>
       </c>
@@ -12300,7 +12304,7 @@
         <v>100380</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A652">
         <v>1210003</v>
       </c>
@@ -12317,7 +12321,7 @@
         <v>155267</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A653">
         <v>1210004</v>
       </c>
@@ -12334,7 +12338,7 @@
         <v>7682637</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654">
         <v>1210004</v>
       </c>
@@ -12351,7 +12355,7 @@
         <v>669827</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655">
         <v>1210004</v>
       </c>
@@ -12368,7 +12372,7 @@
         <v>415673</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A656">
         <v>1210004</v>
       </c>
@@ -12385,7 +12389,7 @@
         <v>36987</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A657">
         <v>1210005</v>
       </c>
@@ -12402,7 +12406,7 @@
         <v>10478153</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A658">
         <v>1210005</v>
       </c>
@@ -12419,7 +12423,7 @@
         <v>1042353</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A659">
         <v>1210005</v>
       </c>
@@ -12450,10 +12454,10 @@
         <v>189</v>
       </c>
       <c r="E660">
-        <v>920173</v>
-      </c>
-    </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A661">
         <v>1210005</v>
       </c>
@@ -12470,7 +12474,7 @@
         <v>1089933</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662">
         <v>1210005</v>
       </c>
@@ -12487,7 +12491,7 @@
         <v>398147</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A663">
         <v>1210005</v>
       </c>
@@ -12504,7 +12508,7 @@
         <v>201530</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664">
         <v>1210005</v>
       </c>
@@ -12521,7 +12525,7 @@
         <v>541360</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A665">
         <v>1210005</v>
       </c>
@@ -12538,7 +12542,7 @@
         <v>55680</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A666">
         <v>1210005</v>
       </c>
@@ -12555,7 +12559,7 @@
         <v>14903</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A667">
         <v>1210006</v>
       </c>
@@ -12572,7 +12576,7 @@
         <v>28403883</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A668">
         <v>1210006</v>
       </c>
@@ -12589,7 +12593,7 @@
         <v>2438113</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A669">
         <v>1210006</v>
       </c>
@@ -12606,7 +12610,7 @@
         <v>24890</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A670">
         <v>1210006</v>
       </c>
@@ -12623,7 +12627,7 @@
         <v>187057</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A671">
         <v>1210006</v>
       </c>
@@ -12640,7 +12644,7 @@
         <v>3067493</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A672">
         <v>1210006</v>
       </c>
@@ -12657,7 +12661,7 @@
         <v>305567</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A673">
         <v>1210006</v>
       </c>
@@ -12674,7 +12678,7 @@
         <v>137937</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674">
         <v>1210006</v>
       </c>
@@ -12691,7 +12695,7 @@
         <v>10760</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A675">
         <v>1210006</v>
       </c>
@@ -12708,7 +12712,7 @@
         <v>37443</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A676">
         <v>1210006</v>
       </c>
@@ -12725,7 +12729,7 @@
         <v>33613</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A677">
         <v>1210006</v>
       </c>
@@ -12742,7 +12746,7 @@
         <v>709350</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678">
         <v>1210006</v>
       </c>
@@ -12759,7 +12763,7 @@
         <v>36160</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A679">
         <v>1210006</v>
       </c>
@@ -12776,7 +12780,7 @@
         <v>33617</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A680">
         <v>1210006</v>
       </c>
@@ -12793,7 +12797,7 @@
         <v>144000</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A681">
         <v>1210006</v>
       </c>
@@ -12810,7 +12814,7 @@
         <v>121883</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A682">
         <v>1210006</v>
       </c>
@@ -12827,7 +12831,7 @@
         <v>1858000</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A683">
         <v>1210006</v>
       </c>
@@ -12844,7 +12848,7 @@
         <v>115593</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A684">
         <v>1210006</v>
       </c>
@@ -12861,7 +12865,7 @@
         <v>11777</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A685">
         <v>1210006</v>
       </c>
@@ -12878,7 +12882,7 @@
         <v>103060</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686">
         <v>1210006</v>
       </c>
@@ -12895,7 +12899,7 @@
         <v>1937203</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687">
         <v>1210006</v>
       </c>
@@ -12912,7 +12916,7 @@
         <v>72887</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688">
         <v>1210006</v>
       </c>
@@ -12929,7 +12933,7 @@
         <v>86637</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A689">
         <v>1210007</v>
       </c>
@@ -12946,7 +12950,7 @@
         <v>-2999447</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A690">
         <v>1210007</v>
       </c>
@@ -12963,7 +12967,7 @@
         <v>27576500</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691">
         <v>1210007</v>
       </c>
@@ -12980,7 +12984,7 @@
         <v>2331080</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A692">
         <v>1210007</v>
       </c>
@@ -12997,7 +13001,7 @@
         <v>20650</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693">
         <v>1210007</v>
       </c>
@@ -13028,10 +13032,10 @@
         <v>189</v>
       </c>
       <c r="E694">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A695">
         <v>1210007</v>
       </c>
@@ -13048,7 +13052,7 @@
         <v>2980310</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A696">
         <v>1210007</v>
       </c>
@@ -13065,7 +13069,7 @@
         <v>426857</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A697">
         <v>1210007</v>
       </c>
@@ -13082,7 +13086,7 @@
         <v>30870</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A698">
         <v>1210007</v>
       </c>
@@ -13099,7 +13103,7 @@
         <v>142537</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A699">
         <v>1210007</v>
       </c>
@@ -13116,7 +13120,7 @@
         <v>6353</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A700">
         <v>1210007</v>
       </c>
@@ -13133,7 +13137,7 @@
         <v>82847</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A701">
         <v>1210007</v>
       </c>
@@ -13150,7 +13154,7 @@
         <v>288283</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A702">
         <v>1210007</v>
       </c>
@@ -13167,7 +13171,7 @@
         <v>152663</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A703">
         <v>1210007</v>
       </c>
@@ -13184,7 +13188,7 @@
         <v>141643</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A704">
         <v>1210007</v>
       </c>
@@ -13201,7 +13205,7 @@
         <v>51867</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A705">
         <v>1210007</v>
       </c>
@@ -13218,7 +13222,7 @@
         <v>11093</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A706">
         <v>1210007</v>
       </c>
@@ -13235,7 +13239,7 @@
         <v>232880</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A707">
         <v>1210007</v>
       </c>
@@ -13252,7 +13256,7 @@
         <v>10023</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A708">
         <v>1210007</v>
       </c>
@@ -13269,7 +13273,7 @@
         <v>316503</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A709">
         <v>1210007</v>
       </c>
@@ -13283,7 +13287,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A710">
         <v>1210008</v>
       </c>
@@ -13300,7 +13304,7 @@
         <v>33740943</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A711">
         <v>1210008</v>
       </c>
@@ -13314,10 +13318,10 @@
         <v>219</v>
       </c>
       <c r="E711">
-        <v>6620783</v>
-      </c>
-    </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A712">
         <v>1210008</v>
       </c>
@@ -13334,7 +13338,7 @@
         <v>2494120</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A713">
         <v>1210008</v>
       </c>
@@ -13351,7 +13355,7 @@
         <v>42650</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A714">
         <v>1210008</v>
       </c>
@@ -13382,10 +13386,10 @@
         <v>189</v>
       </c>
       <c r="E715">
-        <v>846557</v>
-      </c>
-    </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A716">
         <v>1210008</v>
       </c>
@@ -13402,7 +13406,7 @@
         <v>3275967</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A717">
         <v>1210008</v>
       </c>
@@ -13419,7 +13423,7 @@
         <v>2223560</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A718">
         <v>1210008</v>
       </c>
@@ -13436,7 +13440,7 @@
         <v>159203</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A719">
         <v>1210009</v>
       </c>
@@ -13453,7 +13457,7 @@
         <v>3934997</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A720">
         <v>1210009</v>
       </c>
@@ -13470,7 +13474,7 @@
         <v>182687</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A721">
         <v>1210009</v>
       </c>
@@ -13487,7 +13491,7 @@
         <v>325943</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A722">
         <v>1210009</v>
       </c>
@@ -13504,7 +13508,7 @@
         <v>205183</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A723">
         <v>1210009</v>
       </c>
@@ -13521,7 +13525,7 @@
         <v>450020</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A724">
         <v>1210009</v>
       </c>
@@ -13538,7 +13542,7 @@
         <v>12520</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A725">
         <v>1210010</v>
       </c>
@@ -13555,7 +13559,7 @@
         <v>18110180</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A726">
         <v>1210010</v>
       </c>
@@ -13572,7 +13576,7 @@
         <v>4256220</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A727">
         <v>1210010</v>
       </c>
@@ -13589,7 +13593,7 @@
         <v>1385620</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A728">
         <v>1210010</v>
       </c>
@@ -13620,10 +13624,10 @@
         <v>189</v>
       </c>
       <c r="E729">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A730">
         <v>1210010</v>
       </c>
@@ -13640,7 +13644,7 @@
         <v>1735843</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A731">
         <v>1210010</v>
       </c>
@@ -13657,7 +13661,7 @@
         <v>798293</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A732">
         <v>1210010</v>
       </c>
@@ -13674,7 +13678,7 @@
         <v>81057</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A733">
         <v>1210011</v>
       </c>
@@ -13691,7 +13695,7 @@
         <v>42475830</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A734">
         <v>1210011</v>
       </c>
@@ -13705,10 +13709,10 @@
         <v>219</v>
       </c>
       <c r="E734">
-        <v>11349917</v>
-      </c>
-    </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A735">
         <v>1210011</v>
       </c>
@@ -13725,7 +13729,7 @@
         <v>2494120</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A736">
         <v>1210011</v>
       </c>
@@ -13756,10 +13760,10 @@
         <v>189</v>
       </c>
       <c r="E737">
-        <v>1104207</v>
-      </c>
-    </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A738">
         <v>1210011</v>
       </c>
@@ -13776,7 +13780,7 @@
         <v>4527577</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A739">
         <v>1210011</v>
       </c>
@@ -13793,7 +13797,7 @@
         <v>17760</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A740">
         <v>1210011</v>
       </c>
@@ -13810,7 +13814,7 @@
         <v>203327</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A741">
         <v>1210012</v>
       </c>
@@ -13827,7 +13831,7 @@
         <v>21112840</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A742">
         <v>1210012</v>
       </c>
@@ -13844,7 +13848,7 @@
         <v>1526670</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A743">
         <v>1210012</v>
       </c>
@@ -13874,8 +13878,11 @@
       <c r="D744" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A745">
         <v>1210012</v>
       </c>
@@ -13892,7 +13899,7 @@
         <v>2059830</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A746">
         <v>1210012</v>
       </c>
@@ -13909,7 +13916,7 @@
         <v>11743</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A747">
         <v>1210012</v>
       </c>
@@ -13926,7 +13933,7 @@
         <v>96743</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A748">
         <v>1210013</v>
       </c>
@@ -13943,7 +13950,7 @@
         <v>5068700</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A749">
         <v>1210013</v>
       </c>
@@ -13957,10 +13964,10 @@
         <v>219</v>
       </c>
       <c r="E749">
-        <v>1891653</v>
-      </c>
-    </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A750">
         <v>1210013</v>
       </c>
@@ -13977,7 +13984,7 @@
         <v>277123</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A751">
         <v>1210013</v>
       </c>
@@ -13994,7 +14001,7 @@
         <v>20787</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A752">
         <v>1210013</v>
       </c>
@@ -14011,7 +14018,7 @@
         <v>533840</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A753">
         <v>1210013</v>
       </c>
@@ -14028,7 +14035,7 @@
         <v>11247</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A754">
         <v>1210013</v>
       </c>
@@ -14045,7 +14052,7 @@
         <v>1666757</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A755">
         <v>1210013</v>
       </c>
@@ -14062,7 +14069,7 @@
         <v>22320</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A756">
         <v>1210014</v>
       </c>
@@ -14079,7 +14086,7 @@
         <v>20053807</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757">
         <v>1210014</v>
       </c>
@@ -14096,7 +14103,7 @@
         <v>1829047</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A758">
         <v>1210014</v>
       </c>
@@ -14113,7 +14120,7 @@
         <v>122633507</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A759">
         <v>1210014</v>
       </c>
@@ -14130,7 +14137,7 @@
         <v>53947</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A760">
         <v>1210014</v>
       </c>
@@ -14161,10 +14168,10 @@
         <v>189</v>
       </c>
       <c r="E761">
-        <v>662527</v>
-      </c>
-    </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A762">
         <v>1210014</v>
       </c>
@@ -14181,7 +14188,7 @@
         <v>2198833</v>
       </c>
     </row>
-    <row r="763" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A763">
         <v>1210014</v>
       </c>
@@ -14198,7 +14205,7 @@
         <v>248980</v>
       </c>
     </row>
-    <row r="764" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A764">
         <v>1210014</v>
       </c>
@@ -14215,7 +14222,7 @@
         <v>13213077</v>
       </c>
     </row>
-    <row r="765" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A765">
         <v>1210014</v>
       </c>
@@ -14232,7 +14239,7 @@
         <v>1346397</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A766">
         <v>1210014</v>
       </c>
@@ -14249,7 +14256,7 @@
         <v>341526590</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A767">
         <v>1210014</v>
       </c>
@@ -14266,7 +14273,7 @@
         <v>15010577</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A768">
         <v>1210014</v>
       </c>
@@ -14283,7 +14290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A769">
         <v>1210014</v>
       </c>
@@ -14300,7 +14307,7 @@
         <v>102220</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A770">
         <v>1210014</v>
       </c>
@@ -14317,7 +14324,7 @@
         <v>379110</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A771">
         <v>1210014</v>
       </c>
@@ -14334,7 +14341,7 @@
         <v>1737387</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A772">
         <v>1210014</v>
       </c>
@@ -14351,7 +14358,7 @@
         <v>20895010</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A773">
         <v>1210014</v>
       </c>
@@ -14368,7 +14375,7 @@
         <v>4396973</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A774">
         <v>1210014</v>
       </c>
@@ -14385,7 +14392,7 @@
         <v>42950490</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A775">
         <v>1210014</v>
       </c>
@@ -14402,7 +14409,7 @@
         <v>5818043</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A776">
         <v>1210014</v>
       </c>
@@ -14419,7 +14426,7 @@
         <v>11678150</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A777">
         <v>1210014</v>
       </c>
@@ -14436,7 +14443,7 @@
         <v>5232160</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A778">
         <v>1210014</v>
       </c>
@@ -14453,7 +14460,7 @@
         <v>9130</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A779">
         <v>1210014</v>
       </c>
@@ -14470,7 +14477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A780">
         <v>1210014</v>
       </c>
@@ -14487,7 +14494,7 @@
         <v>19803</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A781">
         <v>1210014</v>
       </c>
@@ -14504,7 +14511,7 @@
         <v>36100</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A782">
         <v>1210014</v>
       </c>
@@ -14521,7 +14528,7 @@
         <v>603647</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A783">
         <v>1210014</v>
       </c>
@@ -14538,7 +14545,7 @@
         <v>17359943</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A784">
         <v>1210014</v>
       </c>
@@ -14555,7 +14562,7 @@
         <v>10616923</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A785">
         <v>1210014</v>
       </c>
@@ -14572,7 +14579,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A786">
         <v>1210015</v>
       </c>
@@ -14589,7 +14596,7 @@
         <v>438779193</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A787">
         <v>1210015</v>
       </c>
@@ -14606,7 +14613,7 @@
         <v>40248950</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A788">
         <v>1210015</v>
       </c>
@@ -14623,7 +14630,7 @@
         <v>-14632810</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A789">
         <v>1210016</v>
       </c>
@@ -14640,7 +14647,7 @@
         <v>-44067</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A790">
         <v>1210016</v>
       </c>
@@ -14657,7 +14664,7 @@
         <v>-1410</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A791">
         <v>1210016</v>
       </c>
@@ -14674,7 +14681,7 @@
         <v>-1570</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A792">
         <v>1210017</v>
       </c>
@@ -14691,7 +14698,7 @@
         <v>4186130</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A793">
         <v>1210017</v>
       </c>
@@ -14708,7 +14715,7 @@
         <v>348840</v>
       </c>
     </row>
-    <row r="794" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A794">
         <v>1210017</v>
       </c>
@@ -14725,7 +14732,7 @@
         <v>275023</v>
       </c>
     </row>
-    <row r="795" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A795">
         <v>1210017</v>
       </c>
@@ -14742,7 +14749,7 @@
         <v>20923</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A796">
         <v>1210018</v>
       </c>
@@ -14759,7 +14766,7 @@
         <v>40594677</v>
       </c>
     </row>
-    <row r="797" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A797">
         <v>1210018</v>
       </c>
@@ -14776,7 +14783,7 @@
         <v>3395300</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A798">
         <v>1210019</v>
       </c>
@@ -14793,7 +14800,7 @@
         <v>7622007</v>
       </c>
     </row>
-    <row r="799" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A799">
         <v>1210019</v>
       </c>
@@ -14810,7 +14817,7 @@
         <v>334147</v>
       </c>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A800">
         <v>1210019</v>
       </c>
@@ -14827,7 +14834,7 @@
         <v>806010</v>
       </c>
     </row>
-    <row r="801" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A801">
         <v>1210019</v>
       </c>
@@ -14844,7 +14851,7 @@
         <v>41570</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A802">
         <v>1210019</v>
       </c>
@@ -14861,7 +14868,7 @@
         <v>8313</v>
       </c>
     </row>
-    <row r="803" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A803">
         <v>1210019</v>
       </c>
@@ -14878,7 +14885,7 @@
         <v>31273</v>
       </c>
     </row>
-    <row r="804" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A804">
         <v>1210019</v>
       </c>
@@ -14895,7 +14902,7 @@
         <v>12143</v>
       </c>
     </row>
-    <row r="805" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A805">
         <v>1210019</v>
       </c>
@@ -14912,7 +14919,7 @@
         <v>750487</v>
       </c>
     </row>
-    <row r="806" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A806">
         <v>1210019</v>
       </c>
@@ -14929,7 +14936,7 @@
         <v>14850</v>
       </c>
     </row>
-    <row r="807" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A807">
         <v>1210019</v>
       </c>
@@ -14946,7 +14953,7 @@
         <v>31437</v>
       </c>
     </row>
-    <row r="808" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A808">
         <v>1210019</v>
       </c>
@@ -14963,7 +14970,7 @@
         <v>1401217</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A809">
         <v>1210019</v>
       </c>
@@ -14980,7 +14987,7 @@
         <v>755527</v>
       </c>
     </row>
-    <row r="810" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A810">
         <v>1220001</v>
       </c>
@@ -14994,7 +15001,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A811">
         <v>1220001</v>
       </c>
@@ -15011,7 +15018,7 @@
         <v>7081773</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A812">
         <v>1220001</v>
       </c>
@@ -15028,7 +15035,7 @@
         <v>-2574637</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A813">
         <v>1220002</v>
       </c>
@@ -15045,7 +15052,7 @@
         <v>7058477</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A814">
         <v>1220002</v>
       </c>
@@ -15062,7 +15069,7 @@
         <v>475060</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A815">
         <v>1230001</v>
       </c>
@@ -15079,7 +15086,7 @@
         <v>45496800</v>
       </c>
     </row>
-    <row r="816" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A816">
         <v>1230001</v>
       </c>
@@ -15093,10 +15100,10 @@
         <v>219</v>
       </c>
       <c r="E816">
-        <v>2482793</v>
-      </c>
-    </row>
-    <row r="817" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A817">
         <v>1230001</v>
       </c>
@@ -15113,7 +15120,7 @@
         <v>8036597</v>
       </c>
     </row>
-    <row r="818" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818">
         <v>1230001</v>
       </c>
@@ -15130,7 +15137,7 @@
         <v>748223</v>
       </c>
     </row>
-    <row r="819" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A819">
         <v>1230001</v>
       </c>
@@ -15147,7 +15154,7 @@
         <v>3403050</v>
       </c>
     </row>
-    <row r="820" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A820">
         <v>1230001</v>
       </c>
@@ -15164,7 +15171,7 @@
         <v>208993</v>
       </c>
     </row>
-    <row r="821" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821">
         <v>1230002</v>
       </c>
@@ -15181,7 +15188,7 @@
         <v>173017437</v>
       </c>
     </row>
-    <row r="822" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A822">
         <v>1230002</v>
       </c>
@@ -15198,7 +15205,7 @@
         <v>126032183</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A823">
         <v>1230002</v>
       </c>
@@ -15215,7 +15222,7 @@
         <v>-2817860</v>
       </c>
     </row>
-    <row r="824" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824">
         <v>1230003</v>
       </c>
@@ -15232,7 +15239,7 @@
         <v>2933710</v>
       </c>
     </row>
-    <row r="825" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825">
         <v>1230003</v>
       </c>
@@ -15249,7 +15256,7 @@
         <v>244480</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826">
         <v>1230003</v>
       </c>
@@ -15266,7 +15273,7 @@
         <v>335993</v>
       </c>
     </row>
-    <row r="827" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A827">
         <v>1230003</v>
       </c>
@@ -15283,7 +15290,7 @@
         <v>33506257</v>
       </c>
     </row>
-    <row r="828" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A828">
         <v>1230003</v>
       </c>
@@ -15300,7 +15307,7 @@
         <v>15298727</v>
       </c>
     </row>
-    <row r="829" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829">
         <v>1230003</v>
       </c>
@@ -15317,7 +15324,7 @@
         <v>375431750</v>
       </c>
     </row>
-    <row r="830" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A830">
         <v>1230003</v>
       </c>
@@ -15334,7 +15341,7 @@
         <v>5537000</v>
       </c>
     </row>
-    <row r="831" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A831">
         <v>1230003</v>
       </c>
@@ -15351,7 +15358,7 @@
         <v>42691800</v>
       </c>
     </row>
-    <row r="832" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A832">
         <v>1230003</v>
       </c>
@@ -15368,7 +15375,7 @@
         <v>547710</v>
       </c>
     </row>
-    <row r="833" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833">
         <v>1230003</v>
       </c>
@@ -15385,7 +15392,7 @@
         <v>-1626440</v>
       </c>
     </row>
-    <row r="834" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A834">
         <v>1230003</v>
       </c>
@@ -15402,7 +15409,7 @@
         <v>-11218123</v>
       </c>
     </row>
-    <row r="835" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835">
         <v>1230003</v>
       </c>
@@ -15419,7 +15426,7 @@
         <v>14663</v>
       </c>
     </row>
-    <row r="836" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836">
         <v>1230004</v>
       </c>
@@ -15436,7 +15443,7 @@
         <v>12106910</v>
       </c>
     </row>
-    <row r="837" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837">
         <v>1230004</v>
       </c>
@@ -15450,10 +15457,10 @@
         <v>219</v>
       </c>
       <c r="E837">
-        <v>2837480</v>
-      </c>
-    </row>
-    <row r="838" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A838">
         <v>1230004</v>
       </c>
@@ -15470,7 +15477,7 @@
         <v>1108493</v>
       </c>
     </row>
-    <row r="839" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A839">
         <v>1230004</v>
       </c>
@@ -15501,10 +15508,10 @@
         <v>189</v>
       </c>
       <c r="E840">
-        <v>110420</v>
-      </c>
-    </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A841">
         <v>1230004</v>
       </c>
@@ -15521,7 +15528,7 @@
         <v>910887</v>
       </c>
     </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842">
         <v>1230004</v>
       </c>
@@ -15538,7 +15545,7 @@
         <v>45603</v>
       </c>
     </row>
-    <row r="843" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A843">
         <v>1230005</v>
       </c>
@@ -15555,7 +15562,7 @@
         <v>31903933</v>
       </c>
     </row>
-    <row r="844" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A844">
         <v>1230005</v>
       </c>
@@ -15569,10 +15576,10 @@
         <v>219</v>
       </c>
       <c r="E844">
-        <v>7387810</v>
-      </c>
-    </row>
-    <row r="845" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845">
         <v>1230005</v>
       </c>
@@ -15589,7 +15596,7 @@
         <v>2216993</v>
       </c>
     </row>
-    <row r="846" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A846">
         <v>1230005</v>
       </c>
@@ -15623,7 +15630,7 @@
         <v>736137</v>
       </c>
     </row>
-    <row r="848" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A848">
         <v>1230005</v>
       </c>
@@ -15640,7 +15647,7 @@
         <v>2793037</v>
       </c>
     </row>
-    <row r="849" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849">
         <v>1230005</v>
       </c>
@@ -15657,7 +15664,7 @@
         <v>137567</v>
       </c>
     </row>
-    <row r="850" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A850">
         <v>1230006</v>
       </c>
@@ -15674,7 +15681,7 @@
         <v>22711107</v>
       </c>
     </row>
-    <row r="851" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A851">
         <v>1230006</v>
       </c>
@@ -15688,10 +15695,10 @@
         <v>219</v>
       </c>
       <c r="E851">
-        <v>1891653</v>
-      </c>
-    </row>
-    <row r="852" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A852">
         <v>1230006</v>
       </c>
@@ -15708,7 +15715,7 @@
         <v>1662743</v>
       </c>
     </row>
-    <row r="853" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A853">
         <v>1230006</v>
       </c>
@@ -15725,7 +15732,7 @@
         <v>124707</v>
       </c>
     </row>
-    <row r="854" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854">
         <v>1230006</v>
       </c>
@@ -15742,7 +15749,7 @@
         <v>1793847</v>
       </c>
     </row>
-    <row r="855" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A855">
         <v>1230006</v>
       </c>
@@ -15759,7 +15766,7 @@
         <v>103677</v>
       </c>
     </row>
-    <row r="856" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A856">
         <v>1230007</v>
       </c>
@@ -15776,7 +15783,7 @@
         <v>5613540</v>
       </c>
     </row>
-    <row r="857" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A857">
         <v>1230007</v>
       </c>
@@ -15793,7 +15800,7 @@
         <v>5281353</v>
       </c>
     </row>
-    <row r="858" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858">
         <v>1230008</v>
       </c>
@@ -15810,7 +15817,7 @@
         <v>31353790</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A859">
         <v>1230008</v>
       </c>
@@ -15827,7 +15834,7 @@
         <v>20681290</v>
       </c>
     </row>
-    <row r="860" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A860">
         <v>1230009</v>
       </c>
@@ -15844,7 +15851,7 @@
         <v>12130580</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861">
         <v>1230009</v>
       </c>
@@ -15861,7 +15868,7 @@
         <v>942343</v>
       </c>
     </row>
-    <row r="862" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862">
         <v>1230009</v>
       </c>
@@ -15878,7 +15885,7 @@
         <v>1241353</v>
       </c>
     </row>
-    <row r="863" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A863">
         <v>1230009</v>
       </c>
@@ -15895,7 +15902,7 @@
         <v>55640</v>
       </c>
     </row>
-    <row r="864" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A864">
         <v>1230010</v>
       </c>
@@ -15912,7 +15919,7 @@
         <v>5347343</v>
       </c>
     </row>
-    <row r="865" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A865">
         <v>1230010</v>
       </c>
@@ -15926,7 +15933,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="866" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A866">
         <v>1230010</v>
       </c>
@@ -15943,7 +15950,7 @@
         <v>299780</v>
       </c>
     </row>
-    <row r="867" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A867">
         <v>1230010</v>
       </c>
@@ -15960,7 +15967,7 @@
         <v>30007</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A868">
         <v>1230011</v>
       </c>
@@ -15977,7 +15984,7 @@
         <v>55298190</v>
       </c>
     </row>
-    <row r="869" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A869">
         <v>1230011</v>
       </c>
@@ -15991,10 +15998,10 @@
         <v>219</v>
       </c>
       <c r="E869">
-        <v>4492677</v>
-      </c>
-    </row>
-    <row r="870" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A870">
         <v>1230011</v>
       </c>
@@ -16028,7 +16035,7 @@
         <v>110420</v>
       </c>
     </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A872">
         <v>1230011</v>
       </c>
@@ -16045,7 +16052,7 @@
         <v>5072760</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A873">
         <v>1230011</v>
       </c>
@@ -16062,7 +16069,7 @@
         <v>254653</v>
       </c>
     </row>
-    <row r="874" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A874">
         <v>1230012</v>
       </c>
@@ -16079,7 +16086,7 @@
         <v>153697</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A875">
         <v>1230013</v>
       </c>
@@ -16096,7 +16103,7 @@
         <v>35261380</v>
       </c>
     </row>
-    <row r="876" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A876">
         <v>1230013</v>
       </c>
@@ -16113,7 +16120,7 @@
         <v>1229573</v>
       </c>
     </row>
-    <row r="877" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A877">
         <v>1230014</v>
       </c>
@@ -16130,7 +16137,7 @@
         <v>6180977</v>
       </c>
     </row>
-    <row r="878" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A878">
         <v>1230014</v>
       </c>
@@ -16147,7 +16154,7 @@
         <v>515080</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A879">
         <v>1230014</v>
       </c>
@@ -16164,7 +16171,7 @@
         <v>604630</v>
       </c>
     </row>
-    <row r="880" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A880">
         <v>1230014</v>
       </c>
@@ -16181,7 +16188,7 @@
         <v>30543</v>
       </c>
     </row>
-    <row r="881" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A881">
         <v>1230015</v>
       </c>
@@ -16198,7 +16205,7 @@
         <v>2516190</v>
       </c>
     </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A882">
         <v>1230015</v>
       </c>
@@ -16212,10 +16219,10 @@
         <v>219</v>
       </c>
       <c r="E882">
-        <v>945827</v>
-      </c>
-    </row>
-    <row r="883" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A883">
         <v>1230015</v>
       </c>
@@ -16232,7 +16239,7 @@
         <v>199150</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A884">
         <v>1240001</v>
       </c>
@@ -16249,7 +16256,7 @@
         <v>48491823</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A885">
         <v>1240001</v>
       </c>
@@ -16266,7 +16273,7 @@
         <v>3617310</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A886">
         <v>1240001</v>
       </c>
@@ -16283,7 +16290,7 @@
         <v>-1315103</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A887">
         <v>1240002</v>
       </c>
@@ -16300,7 +16307,7 @@
         <v>-801335239</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A888">
         <v>1240002</v>
       </c>
@@ -16317,7 +16324,7 @@
         <v>-3511896</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A889">
         <v>1240002</v>
       </c>
@@ -16334,7 +16341,7 @@
         <v>-1439387</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A890">
         <v>1240002</v>
       </c>
@@ -16351,7 +16358,7 @@
         <v>-307859588</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A891">
         <v>1240002</v>
       </c>
@@ -16368,7 +16375,7 @@
         <v>-1615059</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A892">
         <v>1240002</v>
       </c>
@@ -16385,7 +16392,7 @@
         <v>-3941739</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A893">
         <v>1240002</v>
       </c>
@@ -16402,7 +16409,7 @@
         <v>313267988</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A894">
         <v>1240002</v>
       </c>
@@ -16419,7 +16426,7 @@
         <v>627514960</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A895">
         <v>1240002</v>
       </c>
@@ -16436,7 +16443,7 @@
         <v>22970328</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A896">
         <v>1240002</v>
       </c>
@@ -16453,7 +16460,7 @@
         <v>72162634</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A897">
         <v>1240002</v>
       </c>
@@ -16470,7 +16477,7 @@
         <v>101684851</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A898">
         <v>1240002</v>
       </c>
@@ -16487,7 +16494,7 @@
         <v>1636647093</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A899">
         <v>1240002</v>
       </c>
@@ -16501,7 +16508,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A900">
         <v>1240002</v>
       </c>
@@ -16518,7 +16525,7 @@
         <v>3146625</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="901" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A901">
         <v>1240002</v>
       </c>
@@ -16535,7 +16542,7 @@
         <v>1936983</v>
       </c>
     </row>
-    <row r="902" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A902">
         <v>1240002</v>
       </c>
@@ -16552,7 +16559,7 @@
         <v>559067</v>
       </c>
     </row>
-    <row r="903" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="903" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A903">
         <v>1240002</v>
       </c>
@@ -16569,7 +16576,7 @@
         <v>19306552</v>
       </c>
     </row>
-    <row r="904" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="904" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A904">
         <v>1240002</v>
       </c>
@@ -16586,7 +16593,7 @@
         <v>12035336</v>
       </c>
     </row>
-    <row r="905" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="905" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A905">
         <v>1240002</v>
       </c>
@@ -16603,7 +16610,7 @@
         <v>140549885</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A906">
         <v>1240002</v>
       </c>
@@ -16620,7 +16627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A907">
         <v>1240002</v>
       </c>
@@ -16637,7 +16644,7 @@
         <v>1544349</v>
       </c>
     </row>
-    <row r="908" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="908" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A908">
         <v>1240002</v>
       </c>
@@ -16654,7 +16661,7 @@
         <v>949572</v>
       </c>
     </row>
-    <row r="909" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="909" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A909">
         <v>1240002</v>
       </c>
@@ -16671,7 +16678,7 @@
         <v>146153</v>
       </c>
     </row>
-    <row r="910" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A910">
         <v>1240002</v>
       </c>
@@ -16688,7 +16695,7 @@
         <v>29744661</v>
       </c>
     </row>
-    <row r="911" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A911">
         <v>1240002</v>
       </c>
@@ -16705,7 +16712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A912">
         <v>1240002</v>
       </c>
@@ -16722,7 +16729,7 @@
         <v>-76796905</v>
       </c>
     </row>
-    <row r="913" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A913">
         <v>1240002</v>
       </c>
@@ -16739,7 +16746,7 @@
         <v>10641360</v>
       </c>
     </row>
-    <row r="914" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A914">
         <v>1240002</v>
       </c>
@@ -16756,7 +16763,7 @@
         <v>335337</v>
       </c>
     </row>
-    <row r="915" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A915">
         <v>1240002</v>
       </c>
@@ -16773,7 +16780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A916">
         <v>1240002</v>
       </c>
@@ -16790,7 +16797,7 @@
         <v>1378513</v>
       </c>
     </row>
-    <row r="917" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A917">
         <v>1240002</v>
       </c>
@@ -16807,16 +16814,24 @@
         <v>19514114</v>
       </c>
     </row>
-    <row r="918" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="D918" t="s">
         <v>271</v>
       </c>
       <c r="E918">
         <f>SUM(E2:E917)</f>
-        <v>8265238618</v>
+        <v>7983517515</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E918" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="(제)복리후생비-포상비"/>
+        <filter val="(판)복리후생비-포상비"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
